--- a/timetable/templates/flow_template.xlsx
+++ b/timetable/templates/flow_template.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,8 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -608,7 +609,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【記入方法】 工程番号は連番(1,2,3...)。前工程番号は複数の場合カンマ区切り(例: 1,2)。  時間決定: 「手動」or「計算」。手動の場合は手動時間(分)に数値を入力。</t>
+          <t>【記入方法】 工程番号は連番(1,2,3...)。前工程番号は複数の場合カンマ区切り(例: 1,2)。  時間決定: 「手動」or「計算」。機器Tag No.: DBに登録された反応槽/フィルターのTag No.を入力（省略可）。</t>
         </is>
       </c>
     </row>
@@ -645,10 +646,15 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>機器Tag No.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -679,10 +685,15 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>R-102</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
           <t>担当A</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>溶剤・原料を仕込む</t>
         </is>
@@ -715,10 +726,15 @@
       <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="6" t="inlineStr">
         <is>
+          <t>R-102</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
           <t>担当A</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>目標温度まで昇温</t>
         </is>
@@ -745,18 +761,25 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
+          <t>手動</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>120</v>
+      </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
+          <t>R-102</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
           <t>担当A</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>反応速度解析より推算</t>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>撹拌反応</t>
         </is>
       </c>
     </row>
@@ -787,10 +810,15 @@
       <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
+          <t>R-102</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
           <t>担当B</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>冷却水で冷却</t>
         </is>
@@ -825,10 +853,15 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
+          <t>R-102</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
           <t>担当B</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>自然冷却晶析</t>
         </is>
@@ -861,10 +894,15 @@
       <c r="F9" s="6" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
+          <t>F-102</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
           <t>担当B</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>加圧ろ過</t>
         </is>
@@ -899,10 +937,15 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
+          <t>F-102</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
           <t>担当B</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>洗液3回</t>
         </is>
@@ -929,16 +972,23 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr"/>
+          <t>手動</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>90</v>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
+          <t>R-103</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
           <t>担当C</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>溶媒回収</t>
         </is>
@@ -971,12 +1021,13 @@
       <c r="F12" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>担当C</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>製品タンクへ移液</t>
         </is>
@@ -984,15 +1035,18 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="C4:C100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"CHARGE,HEAT,COOL,REACTION,CONCENTRATE,FILTER,TRANSFER,WASH,OTHER"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"手動,計算"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"R-101,R-102,R-103,R-104,R-105,F-101,F-102,F-201,C-101,C-201"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/timetable/templates/flow_template.xlsx
+++ b/timetable/templates/flow_template.xlsx
@@ -477,17 +477,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -500,49 +496,29 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【記入方法】 工程番号は連番(1,2,3...)。前工程番号は複数の場合カンマ区切り(例: 1,2)。  時間決定: 「手動」or「計算」。機器Tag No.: DBに登録された反応槽/フィルターのTag No.を入力（省略可）。  計算工程のパラメータはアプリ画面で直接入力してください。</t>
+          <t>【記入方法】 操作番号は連番(1,2,3...)。前操作番号は複数の場合カンマ区切り(例: 1,2)。  機器・時間の設定はアプリ画面(③)で行ってください。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>工程番号</t>
+          <t>操作番号</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>工程名</t>
+          <t>操作名</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>前操作番号</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>操作タイプ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>前工程番号</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>時間決定</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>手動時間(分)</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>機器Tag No.</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>備考</t>
         </is>
       </c>
     </row>
@@ -555,28 +531,10 @@
           <t>原料仕込み</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>CHARGE</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>手動</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>R-102</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>溶剤・原料を仕込む</t>
         </is>
       </c>
     </row>
@@ -591,28 +549,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
           <t>HEAT</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>R-102</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>目標温度まで昇温</t>
         </is>
       </c>
     </row>
@@ -627,30 +569,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>REACTION</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>手動</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>R-102</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>撹拌反応</t>
         </is>
       </c>
     </row>
@@ -665,28 +589,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
           <t>COOL</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>R-102</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>冷却水で冷却</t>
         </is>
       </c>
     </row>
@@ -701,30 +609,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>手動</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>R-102</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>自然冷却晶析</t>
+          <t>CRYSTALLIZATION</t>
         </is>
       </c>
     </row>
@@ -739,28 +629,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
           <t>FILTER</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>F-102</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>加圧ろ過</t>
         </is>
       </c>
     </row>
@@ -775,30 +649,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>WASH</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>手動</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>F-102</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>洗液3回</t>
         </is>
       </c>
     </row>
@@ -813,30 +669,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
           <t>CONCENTRATE</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>手動</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>R-103</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>溶媒回収</t>
         </is>
       </c>
     </row>
@@ -851,43 +689,23 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>TRANSFER</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>手動</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>製品タンクへ移液</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="C4:C100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"CHARGE,HEAT,COOL,REACTION,CONCENTRATE,FILTER,TRANSFER,WASH,OTHER"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E4:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"手動,計算"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"R-101,R-102,R-103,R-104,R-105,F-101,F-102,F-201,C-101,C-201"</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="D4:D100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"CHARGE,HEAT,COOL,REACTION,CONCENTRATE,FILTER,TRANSFER,WASH,SEPARATION,CRYSTALLIZATION,OTHER"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
